--- a/internal_doc/05.测试设计/story/mysql连接器/5.7.25测试用例差别.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/5.7.25测试用例差别.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
   <si>
     <t>compare.result</t>
   </si>
@@ -29,30 +29,15 @@
     <t>create.result</t>
   </si>
   <si>
-    <t>ctype_uca.result</t>
-  </si>
-  <si>
     <t>range_all.result</t>
   </si>
   <si>
-    <t>range_icp_mrr.result</t>
-  </si>
-  <si>
-    <t>range_icp.result</t>
-  </si>
-  <si>
     <t>range_mrr_cost.result</t>
   </si>
   <si>
     <t>range_mrr.result</t>
   </si>
   <si>
-    <t>temporal_literal.result</t>
-  </si>
-  <si>
-    <t>type_temporal_fractional.result</t>
-  </si>
-  <si>
     <t>是否影响github用例</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -70,18 +55,6 @@
   </si>
   <si>
     <t>是</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ctype_many.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>未修改</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>执行create table t1 (b char(0));insert into t1 values (""),(null);报错 : duplicate key in table 't1'，用例退出。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -100,10 +73,6 @@
     <t>否是已修改</t>
   </si>
   <si>
-    <t>当SET sql_mode=default，创建表时列为datetime类型，SHOW CREATE TABLE t1;无默认值项： DEFAULT '0000-00-00 00:00:00 '</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>备注</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -112,107 +81,131 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>5.7.25 utf8mb4和utf32开始支持其他所有Unicode编码，用例预期结果改变，直接退出。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>测试文件末尾，5.7.25多了测试步骤</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>测试文件末尾，5.7.25多了测试步骤，同时多告警信息</t>
+    <t>mysql--help-win.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>range_none.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤多了头文件，测试结果相同</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.25修改了预期结果</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.25修改了预期结果（个别参数不同）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤相同，5.7.25修改了预期结果，同时多告警信息</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>未修改用例</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql引擎未通过用例</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysql--help-notwin.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ctype_many.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>flush_read_lock.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysqlpump_partial_bkp.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysql_config_editor.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>opt_hints.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>partition_exchange.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>range_with_memory_limit.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>temporal_literal.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_temporal_fractional.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.7.25 utf8mb4和utf32开始支持其他所有Unicode编码，用例预期结果改变，直接退出。(用例预期结果改变导致)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>当SET sql_mode=default，创建表时列为datetime类型，SHOW CREATE TABLE t1;无默认值项： DEFAULT '0000-00-00 00:00:00 '(用例预期结果改变导致)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ctype_many.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>temporal_literal.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_temporal_fractional.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>已同步</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>已同步</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试文件末尾，5.7.25多了测试步骤</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>mysql--help-win.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>range_none.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤不同，5.7.25 utf8mb4和utf32开始支持其他所有Unicode编码，修改了ERROR信息</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤不同，测试结果略微差异（多了两行注释）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤多了头文件，测试结果相同</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.25修改了预期结果</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.25修改了预期结果（个别参数不同）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.25修改了预期结果，同时多告警信息</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>未修改用例</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql引擎未通过用例</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试步骤相同，5.7.25修改了预期结果,与"sql引擎未通过用例"表中描述一致</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>当SET sql_mode=default，创建表时列为datetime类型，SHOW CREATE TABLE t1;无默认值项： DEFAULT '0000-00-00 00:00:00 '</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>mysql--help-notwin.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ctype_many.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>flush_read_lock.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>mysqlpump_partial_bkp.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>mysql_config_editor.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>opt_hints.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>partition_exchange.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>range_with_memory_limit.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>temporal_literal.result</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_temporal_fractional.result</t>
+    <t>range_icp.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>range_icp_mrr.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ctype_uca.result</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试步骤不同，在std_data目录下新增了数据文件</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1201,16 +1194,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
@@ -1218,240 +1211,264 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="30" hidden="1" customHeight="1">
       <c r="A22"/>
@@ -3172,7 +3189,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3192,7 +3209,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3214,7 +3231,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3225,67 +3242,56 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.75" customWidth="1"/>
-    <col min="2" max="2" width="57.625" customWidth="1"/>
-    <col min="3" max="3" width="32.125" customWidth="1"/>
+    <col min="2" max="2" width="69" customWidth="1"/>
+    <col min="3" max="3" width="61.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
